--- a/Classification Agent Test Dataset.xlsx
+++ b/Classification Agent Test Dataset.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="170">
   <si>
     <t>Category</t>
   </si>
@@ -325,9 +325,6 @@
     <t>Our team wants software that produces draft captions and transcripts for teachers. How can the interface help teachers correct terminology, speaker labels, and timing efficiently before publishing?</t>
   </si>
   <si>
-    <t>I am building a teaching dashboard that shows whether captioning or transcription services are failing during live classes. Which operational indicators should teachers see in real time?</t>
-  </si>
-  <si>
     <t>We are creating an AI assistant that turns spoken classroom explanations into visual summaries for students with hearing impairment. How should teachers verify that key meaning, examples, and emphasis have been preserved?</t>
   </si>
   <si>
@@ -499,10 +496,10 @@
     <t>I am building a regional education technology platform that must operate across urban, rural, and geographically isolated schools. What architecture and deployment model would maximize resilience and maintainability?</t>
   </si>
   <si>
+    <t>I am developing an AI-powered learning platform for students in remote and rural communities where internet connectivity is often unstable. How can I design the system to provide personalized learning support while ensuring that students can continue learning offline and synchronize their progress when connectivity is restored?</t>
+  </si>
+  <si>
     <t>We want an analytics system to compare technology-supported learning across regions with different infrastructure. How should benchmarking account for unequal connectivity, staffing, and device availability?</t>
-  </si>
-  <si>
-    <t>A2:B152</t>
   </si>
   <si>
     <t>I am designing procurement and rollout software for a multi-region education program. How should site readiness, local technical support, data synchronization, and disaster recovery be tracked before expansion?</t>
@@ -727,7 +724,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -737,6 +734,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1059,7 +1062,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1083,16 +1086,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1101,93 +1104,96 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1673,8 +1679,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D151"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
+  <dimension ref="A1:B151"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="53" customWidth="1"/>
     <col min="2" max="2" width="100" customWidth="1"/>
@@ -2418,15 +2424,15 @@
     </row>
     <row r="93" ht="54" customHeight="1" spans="1:2">
       <c r="A93" s="2" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="94" ht="54" customHeight="1" spans="1:2">
       <c r="A94" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>104</v>
@@ -2434,7 +2440,7 @@
     </row>
     <row r="95" ht="54" customHeight="1" spans="1:2">
       <c r="A95" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>105</v>
@@ -2442,7 +2448,7 @@
     </row>
     <row r="96" ht="54" customHeight="1" spans="1:2">
       <c r="A96" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>106</v>
@@ -2450,7 +2456,7 @@
     </row>
     <row r="97" ht="54" customHeight="1" spans="1:2">
       <c r="A97" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>107</v>
@@ -2458,7 +2464,7 @@
     </row>
     <row r="98" ht="54" customHeight="1" spans="1:2">
       <c r="A98" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>108</v>
@@ -2466,7 +2472,7 @@
     </row>
     <row r="99" ht="54" customHeight="1" spans="1:2">
       <c r="A99" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>109</v>
@@ -2474,15 +2480,15 @@
     </row>
     <row r="100" ht="54" customHeight="1" spans="1:2">
       <c r="A100" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="101" ht="54" customHeight="1" spans="1:2">
       <c r="A101" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>112</v>
@@ -2490,7 +2496,7 @@
     </row>
     <row r="102" ht="54" customHeight="1" spans="1:2">
       <c r="A102" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>113</v>
@@ -2498,7 +2504,7 @@
     </row>
     <row r="103" ht="54" customHeight="1" spans="1:2">
       <c r="A103" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>114</v>
@@ -2506,7 +2512,7 @@
     </row>
     <row r="104" ht="54" customHeight="1" spans="1:2">
       <c r="A104" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>115</v>
@@ -2514,7 +2520,7 @@
     </row>
     <row r="105" ht="54" customHeight="1" spans="1:2">
       <c r="A105" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>116</v>
@@ -2522,15 +2528,15 @@
     </row>
     <row r="106" ht="54" customHeight="1" spans="1:2">
       <c r="A106" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="107" ht="54" customHeight="1" spans="1:2">
       <c r="A107" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>119</v>
@@ -2538,7 +2544,7 @@
     </row>
     <row r="108" ht="54" customHeight="1" spans="1:2">
       <c r="A108" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>120</v>
@@ -2546,7 +2552,7 @@
     </row>
     <row r="109" ht="54" customHeight="1" spans="1:2">
       <c r="A109" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>121</v>
@@ -2554,7 +2560,7 @@
     </row>
     <row r="110" ht="54" customHeight="1" spans="1:2">
       <c r="A110" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>122</v>
@@ -2562,7 +2568,7 @@
     </row>
     <row r="111" ht="54" customHeight="1" spans="1:2">
       <c r="A111" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>123</v>
@@ -2570,7 +2576,7 @@
     </row>
     <row r="112" ht="54" customHeight="1" spans="1:2">
       <c r="A112" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>124</v>
@@ -2578,7 +2584,7 @@
     </row>
     <row r="113" ht="54" customHeight="1" spans="1:2">
       <c r="A113" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>125</v>
@@ -2586,15 +2592,15 @@
     </row>
     <row r="114" ht="54" customHeight="1" spans="1:2">
       <c r="A114" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="115" ht="54" customHeight="1" spans="1:2">
       <c r="A115" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>128</v>
@@ -2602,7 +2608,7 @@
     </row>
     <row r="116" ht="54" customHeight="1" spans="1:2">
       <c r="A116" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>129</v>
@@ -2610,7 +2616,7 @@
     </row>
     <row r="117" ht="54" customHeight="1" spans="1:2">
       <c r="A117" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>130</v>
@@ -2618,7 +2624,7 @@
     </row>
     <row r="118" ht="54" customHeight="1" spans="1:2">
       <c r="A118" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>131</v>
@@ -2626,23 +2632,23 @@
     </row>
     <row r="119" ht="54" customHeight="1" spans="1:2">
       <c r="A119" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="120" ht="54" customHeight="1" spans="1:2">
-      <c r="A120" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B120" s="2" t="s">
+      <c r="A120" s="3" t="s">
         <v>133</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="121" ht="54" customHeight="1" spans="1:2">
       <c r="A121" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>135</v>
@@ -2650,7 +2656,7 @@
     </row>
     <row r="122" ht="54" customHeight="1" spans="1:2">
       <c r="A122" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>136</v>
@@ -2658,7 +2664,7 @@
     </row>
     <row r="123" ht="54" customHeight="1" spans="1:2">
       <c r="A123" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>137</v>
@@ -2666,7 +2672,7 @@
     </row>
     <row r="124" ht="54" customHeight="1" spans="1:2">
       <c r="A124" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>138</v>
@@ -2674,15 +2680,15 @@
     </row>
     <row r="125" ht="54" customHeight="1" spans="1:2">
       <c r="A125" s="2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="126" ht="54" customHeight="1" spans="1:2">
       <c r="A126" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>141</v>
@@ -2690,7 +2696,7 @@
     </row>
     <row r="127" ht="54" customHeight="1" spans="1:2">
       <c r="A127" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>142</v>
@@ -2698,197 +2704,194 @@
     </row>
     <row r="128" ht="54" customHeight="1" spans="1:2">
       <c r="A128" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="129" ht="54" customHeight="1" spans="1:4">
+    <row r="129" ht="54" customHeight="1" spans="1:2">
       <c r="A129" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="130" ht="54" customHeight="1" spans="1:4">
+    <row r="130" ht="54" customHeight="1" spans="1:2">
       <c r="A130" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="131" ht="54" customHeight="1" spans="1:4">
+    <row r="131" ht="54" customHeight="1" spans="1:2">
       <c r="A131" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="132" ht="54" customHeight="1" spans="1:4">
+    <row r="132" ht="54" customHeight="1" spans="1:2">
       <c r="A132" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B132" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="133" ht="54" customHeight="1" spans="1:2">
+      <c r="A133" s="2" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="133" ht="54" customHeight="1" spans="1:4">
-      <c r="A133" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="134" ht="54" customHeight="1" spans="1:4">
+    <row r="134" ht="54" customHeight="1" spans="1:2">
       <c r="A134" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="135" ht="54" customHeight="1" spans="1:4">
+    <row r="135" ht="54" customHeight="1" spans="1:2">
       <c r="A135" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="136" ht="54" customHeight="1" spans="1:4">
+    <row r="136" ht="54" customHeight="1" spans="1:2">
       <c r="A136" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="137" ht="54" customHeight="1" spans="1:4">
+    <row r="137" ht="54" customHeight="1" spans="1:2">
       <c r="A137" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="138" ht="54" customHeight="1" spans="1:4">
+    <row r="138" ht="54" customHeight="1" spans="1:2">
       <c r="A138" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="139" ht="54" customHeight="1" spans="1:4">
+    <row r="139" ht="54" customHeight="1" spans="1:2">
       <c r="A139" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D139" t="s">
+    </row>
+    <row r="140" ht="54" customHeight="1" spans="1:2">
+      <c r="A140" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="140" ht="54" customHeight="1" spans="1:4">
-      <c r="A140" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B140" s="2" t="s">
+    <row r="141" ht="54" customHeight="1" spans="1:2">
+      <c r="A141" s="2" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="141" ht="54" customHeight="1" spans="1:4">
-      <c r="A141" s="2" t="s">
+      <c r="B141" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B141" s="2" t="s">
+    </row>
+    <row r="142" ht="54" customHeight="1" spans="1:2">
+      <c r="A142" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B142" s="2" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="142" ht="54" customHeight="1" spans="1:4">
-      <c r="A142" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B142" s="2" t="s">
+    <row r="143" ht="54" customHeight="1" spans="1:2">
+      <c r="A143" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B143" s="2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="143" ht="54" customHeight="1" spans="1:4">
-      <c r="A143" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B143" s="2" t="s">
+    <row r="144" ht="54" customHeight="1" spans="1:2">
+      <c r="A144" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B144" s="2" t="s">
         <v>161</v>
-      </c>
-    </row>
-    <row r="144" ht="54" customHeight="1" spans="1:4">
-      <c r="A144" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="145" ht="54" customHeight="1" spans="1:2">
       <c r="A145" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="146" ht="54" customHeight="1" spans="1:2">
       <c r="A146" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B146" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="147" ht="54" customHeight="1" spans="1:2">
       <c r="A147" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="148" ht="54" customHeight="1" spans="1:2">
       <c r="A148" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="149" ht="54" customHeight="1" spans="1:2">
       <c r="A149" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="150" ht="54" customHeight="1" spans="1:2">
       <c r="A150" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B150" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="151" ht="25.5" spans="1:2">
+      <c r="A151" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>169</v>
-      </c>
-    </row>
-    <row r="151" ht="54" customHeight="1" spans="1:2">
-      <c r="A151" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>170</v>
       </c>
     </row>
   </sheetData>
